--- a/history/volume_history_DPEN_True.xlsx
+++ b/history/volume_history_DPEN_True.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.109411128</v>
+        <v>0.109278</v>
       </c>
       <c r="C2" t="n">
         <v>0.02754968404769897</v>
@@ -461,9 +461,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.056285172</v>
+        <v>0.05705787500000001</v>
       </c>
       <c r="C3" t="n">
+        <v>0.02754968404769897</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.040700625</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.02754968404769897</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.03390750000000001</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.02754968404769897</v>
       </c>
     </row>
